--- a/ksoft_old/docs/records/Operation_Code_No_Finance_Mov_Records.xlsx
+++ b/ksoft_old/docs/records/Operation_Code_No_Finance_Mov_Records.xlsx
@@ -5582,13 +5582,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5F2AF595-D6EF-4097-BB4B-308D5C75FDC8}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8E7308BD-5578-45BE-9E01-CFA77A0E00F8}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{86100CFE-339D-42AE-8A3D-5F6C7AE41ECF}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{149524D1-11AF-4165-AB02-D98FA8275329}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{003D39B8-FAE5-498A-9EEC-8B06BD1FBA46}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4C876D32-573D-41F2-9DC2-4ABE99AA6B78}"/>
 </file>
--- a/ksoft_old/docs/records/Operation_Code_No_Finance_Mov_Records.xlsx
+++ b/ksoft_old/docs/records/Operation_Code_No_Finance_Mov_Records.xlsx
@@ -5582,13 +5582,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8E7308BD-5578-45BE-9E01-CFA77A0E00F8}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D860C1CD-EEB9-49AE-B35C-B62A7F8F3590}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{149524D1-11AF-4165-AB02-D98FA8275329}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{236BBFB4-A4ED-408E-90C8-C48CF22F2135}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4C876D32-573D-41F2-9DC2-4ABE99AA6B78}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E3547883-26BB-4CA9-AE10-2E799921690D}"/>
 </file>
--- a/ksoft_old/docs/records/Operation_Code_No_Finance_Mov_Records.xlsx
+++ b/ksoft_old/docs/records/Operation_Code_No_Finance_Mov_Records.xlsx
@@ -5582,13 +5582,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D860C1CD-EEB9-49AE-B35C-B62A7F8F3590}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5F2AF595-D6EF-4097-BB4B-308D5C75FDC8}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{236BBFB4-A4ED-408E-90C8-C48CF22F2135}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{86100CFE-339D-42AE-8A3D-5F6C7AE41ECF}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E3547883-26BB-4CA9-AE10-2E799921690D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{003D39B8-FAE5-498A-9EEC-8B06BD1FBA46}"/>
 </file>